--- a/дом качества — экономичная термокружка для студентов.xlsx
+++ b/дом качества — экономичная термокружка для студентов.xlsx
@@ -1135,6 +1135,11 @@
       <c r="E5" s="27" t="n"/>
       <c r="F5" s="35" t="n"/>
       <c r="G5" s="69" t="n"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J5" s="70" t="inlineStr">
         <is>
           <t>Положительно</t>
@@ -1165,7 +1170,16 @@
       <c r="D6" s="69" t="n"/>
       <c r="E6" s="27" t="n"/>
       <c r="F6" s="35" t="n"/>
-      <c r="G6" s="69" t="n"/>
+      <c r="G6" s="69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
       <c r="K6" s="31" t="n"/>
       <c r="L6" s="32" t="n"/>
     </row>
@@ -1174,8 +1188,21 @@
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="69" t="n"/>
       <c r="E7" s="27" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="69" t="n"/>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="69" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
       <c r="J7" s="71" t="inlineStr">
         <is>
           <t>Соотношение:</t>
@@ -1188,10 +1215,26 @@
       <c r="B8" s="69" t="n"/>
       <c r="C8" s="27" t="n"/>
       <c r="D8" s="69" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="35" t="n"/>
-      <c r="G8" s="69" t="n"/>
-      <c r="H8" s="27" t="n"/>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G8" s="69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J8" s="33" t="n">
         <v>9</v>
       </c>
@@ -1931,7 +1974,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Приоритеты улучшения: удержание тепла, герметичность/эргономика крышки и снижение цены при сохранении прочности и экологичности.</t>
+          <t>Приоритеты улучшения: максимизировать сохранение тепла и надежность герметичной крышки, затем снижать цену без потери прочности и экологичности материалов.</t>
         </is>
       </c>
     </row>

--- a/дом качества — экономичная термокружка для студентов.xlsx
+++ b/дом качества — экономичная термокружка для студентов.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Дом качества" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Инструкция" sheetId="4" r:id="rId1"/>
+    <sheet name="Дом качества" sheetId="3" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
@@ -16,138 +22,248 @@
     <definedName name="Correlation_Options">'[1]Data Validation Sources'!$C$2:$C$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Дом качества'!$A$1:$N$33</definedName>
   </definedNames>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>Comments/Conclusion:</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Дом качества</t>
+  </si>
+  <si>
+    <t>Корелляция:</t>
+  </si>
+  <si>
+    <t>Название проекта:</t>
+  </si>
+  <si>
+    <t>Рук.проекта:</t>
+  </si>
+  <si>
+    <t>Дата:</t>
+  </si>
+  <si>
+    <t>Положительно</t>
+  </si>
+  <si>
+    <t>Этап (КТ)</t>
+  </si>
+  <si>
+    <t>Нет зависимости</t>
+  </si>
+  <si>
+    <t>Отрицательно</t>
+  </si>
+  <si>
+    <t>Оценка: Слабо: 1, Сильно: 5</t>
+  </si>
+  <si>
+    <t>Сильно</t>
+  </si>
+  <si>
+    <t>Средне</t>
+  </si>
+  <si>
+    <t>Слабо</t>
+  </si>
+  <si>
+    <t>Отсутствует</t>
+  </si>
+  <si>
+    <t>Соотношение:</t>
+  </si>
+  <si>
+    <t>2. Важность для
+потребителя</t>
+  </si>
+  <si>
+    <t>Мин.: 1,
+Макс.: 5</t>
+  </si>
+  <si>
+    <t>Направления улучшений (↑,0,↓)</t>
+  </si>
+  <si>
+    <t>3. Функциональные требования
+→</t>
+  </si>
+  <si>
+    <t>1. Требования потребителя
+↓</t>
+  </si>
+  <si>
+    <t>Техническая важность (расчет)</t>
+  </si>
+  <si>
+    <t>Важность, %</t>
+  </si>
+  <si>
+    <t>Приоритетность (топ n)</t>
+  </si>
+  <si>
+    <t>Приоритет для улучшения</t>
+  </si>
+  <si>
+    <t>Конкурент 1</t>
+  </si>
+  <si>
+    <t>Конкурент 2</t>
+  </si>
+  <si>
+    <t>Конкурент 3</t>
+  </si>
+  <si>
+    <t>Коеф конкурентоспособности ИО</t>
+  </si>
+  <si>
+    <t>Исслед. Обр</t>
+  </si>
+  <si>
+    <t>Сумма соотношений при Ki&lt;0,7</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="17">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color theme="1" tint="0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF0000CC"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF0000CC"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1" tint="0.499984740745262"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1" tint="0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color indexed="55"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color indexed="55"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="20"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="20"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1" tint="0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1" tint="0.249977111117893"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -159,7 +275,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -182,7 +298,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -195,38 +311,38 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top/>
       <bottom/>
@@ -236,7 +352,7 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -244,64 +360,64 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </left>
       <right/>
       <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -310,19 +426,19 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top/>
       <bottom/>
@@ -423,277 +539,954 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="79">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <mruColors>
+      <color rgb="FFEAEAEA"/>
+      <color rgb="FFCCFFFF"/>
+      <color rgb="FFC3E1FF"/>
+      <color rgb="FF99CCFF"/>
+      <color rgb="FF0000CC"/>
+      <color rgb="FFFFFF99"/>
+      <color rgb="FF66FFFF"/>
+      <color rgb="FFCCFFCC"/>
+      <color rgb="FFFFFFCC"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>13</xdr:col>
+          <xdr:colOff>476250</xdr:colOff>
+          <xdr:row>171</xdr:row>
+          <xdr:rowOff>85725</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3073" name="Object 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s3073"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000010C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="Group 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B156685-2A27-4A0C-9648-80CBFA59D42F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr>
+          <a:grpSpLocks/>
+        </xdr:cNvGrpSpPr>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3055327" y="337038"/>
+          <a:ext cx="3590192" cy="1333500"/>
+          <a:chOff x="364" y="70"/>
+          <a:chExt cx="376" cy="134"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="3" name="AutoShape 32">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA097E01-E960-4D37-8C1E-E42C7F1D26F4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="364" y="70"/>
+            <a:ext cx="376" cy="134"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 50000"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="12700">
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="65000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+            <a:headEnd/>
+            <a:tailEnd/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="4" name="Rectangle 33">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC46ACEC-B134-41EF-9363-75B36072A091}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="422" y="167"/>
+            <a:ext cx="33" cy="19"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+            <a:headEnd/>
+            <a:tailEnd/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="36576" bIns="0" anchor="t" upright="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1000"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>.</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="5" name="Rectangle 34">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F445F93D-0207-4BAD-A46F-CBDD5B350CB1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="459" y="140"/>
+            <a:ext cx="33" cy="19"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+            <a:headEnd/>
+            <a:tailEnd/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="36576" bIns="0" anchor="t" upright="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1000"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>.</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="Rectangle 35">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7255F346-0704-421E-BAFD-EEE1EF4A17F1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="497" y="167"/>
+            <a:ext cx="33" cy="19"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+            <a:headEnd/>
+            <a:tailEnd/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="36576" bIns="0" anchor="t" upright="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1000"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>.</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="7" name="Rectangle 36">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5996035-003B-4D9E-B94F-4417897412A7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="497" y="115"/>
+            <a:ext cx="33" cy="19"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+            <a:headEnd/>
+            <a:tailEnd/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="36576" bIns="0" anchor="t" upright="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1000"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>.</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="8" name="Rectangle 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E639F52-1E22-4CEB-A7A8-F1A3D4CF6BC6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="534" y="141"/>
+            <a:ext cx="33" cy="19"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+            <a:headEnd/>
+            <a:tailEnd/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="36576" bIns="0" anchor="t" upright="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1000"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>.</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="9" name="Rectangle 38">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5FAB9E3-E8D9-4D7E-A853-1CB61AAB9D83}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="571" y="167"/>
+            <a:ext cx="33" cy="19"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+            <a:headEnd/>
+            <a:tailEnd/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="36576" bIns="0" anchor="t" upright="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1000"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>.</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="10" name="Rectangle 39">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06D06632-60DE-41BD-B23C-F9FD073DB76E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="534" y="87"/>
+            <a:ext cx="33" cy="19"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+            <a:headEnd/>
+            <a:tailEnd/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="36576" bIns="0" anchor="t" upright="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1000"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>.</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="11" name="Rectangle 40">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C93907D5-8D39-4998-A613-88DD577C5D65}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="571" y="114"/>
+            <a:ext cx="33" cy="19"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+            <a:headEnd/>
+            <a:tailEnd/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="36576" bIns="0" anchor="t" upright="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1000"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>.</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="12" name="Rectangle 41">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4A81D42-7B69-44F9-B33E-E667C59C422C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="609" y="140"/>
+            <a:ext cx="33" cy="19"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+            <a:headEnd/>
+            <a:tailEnd/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="36576" bIns="0" anchor="t" upright="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1000"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>.</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="13" name="Rectangle 42">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35E9C955-50B0-4E95-B84E-E20B4E727DE4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr>
+            <a:spLocks noChangeArrowheads="1"/>
+          </xdr:cNvSpPr>
+        </xdr:nvSpPr>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="647" y="167"/>
+            <a:ext cx="33" cy="19"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln w="9525">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+            <a:headEnd/>
+            <a:tailEnd/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="36576" bIns="0" anchor="t" upright="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1000"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>.</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="House of Quality 1"/>
       <sheetName val="Data Validation Sources"/>
@@ -1021,237 +1814,233 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="69" fitToHeight="0"/>
+  <pageSetup paperSize="9" scale="69" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <oleObjects>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Visio.Drawing.15" shapeId="3073" r:id="rId4">
+          <objectPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>13</xdr:col>
+                <xdr:colOff>476250</xdr:colOff>
+                <xdr:row>171</xdr:row>
+                <xdr:rowOff>85725</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Visio.Drawing.15" shapeId="3073" r:id="rId4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </oleObjects>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac">
   <dimension ref="A1:M40"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12" ns2:dyDescent="0.2"/>
   <cols>
-    <col width="2.7109375" customWidth="1" style="26" min="1" max="1"/>
-    <col width="12.28515625" customWidth="1" style="26" min="2" max="2"/>
-    <col width="30.7109375" customWidth="1" style="26" min="3" max="3"/>
-    <col width="10.7109375" customWidth="1" style="26" min="4" max="9"/>
-    <col width="11.5703125" customWidth="1" style="26" min="10" max="13"/>
-    <col width="2.7109375" customWidth="1" style="26" min="14" max="14"/>
-    <col width="8.85546875" customWidth="1" style="26" min="15" max="16384"/>
+    <col min="1" max="1" width="2.7109375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" style="8" customWidth="1"/>
+    <col min="4" max="9" width="10.7109375" style="8" customWidth="1"/>
+    <col min="10" max="13" width="11.5703125" style="8" customWidth="1"/>
+    <col min="14" max="14" width="2.7109375" style="8" customWidth="1"/>
+    <col min="15" max="16384" width="8.85546875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.25" customHeight="1">
-      <c r="B1" s="47" t="inlineStr">
-        <is>
-          <t>Дом качества</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="69" t="n"/>
-      <c r="G2" s="27" t="n"/>
-      <c r="H2" s="27" t="n"/>
-      <c r="K2" s="28" t="n"/>
-      <c r="L2" s="29" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="B3" s="69" t="inlineStr">
-        <is>
-          <t>Название проекта:</t>
-        </is>
+    <row r="1" spans="1:13" ht="26.25" ns2:dyDescent="0.4">
+      <c r="B1" s="47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="B2" s="3"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="29"/>
+    </row>
+    <row r="3" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="B3" s="69" t="s">
+        <v>6</v>
       </c>
       <c r="C3" s="61" t="inlineStr">
         <is>
           <t>Экономичная термокружка для студентов</t>
         </is>
       </c>
-      <c r="D3" s="69" t="n"/>
-      <c r="E3" s="27" t="n"/>
-      <c r="F3" s="35" t="n"/>
-      <c r="G3" s="69" t="n"/>
-      <c r="J3" s="62" t="inlineStr">
-        <is>
-          <t>Корелляция:</t>
-        </is>
-      </c>
-      <c r="K3" s="31" t="n"/>
-      <c r="L3" s="32" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="69" t="inlineStr">
-        <is>
-          <t>Рук.проекта:</t>
-        </is>
+      <c r="D3" s="3"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="3"/>
+      <c r="J3" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="31"/>
+      <c r="L3" s="32"/>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="B4" s="69" t="s">
+        <v>7</v>
       </c>
       <c r="C4" s="61" t="inlineStr">
         <is>
           <t>Студент</t>
         </is>
       </c>
-      <c r="D4" s="69" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="35" t="n"/>
-      <c r="G4" s="69" t="n"/>
-      <c r="J4" s="63" t="inlineStr">
+      <c r="D4" s="3"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="3"/>
+      <c r="J4" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="63" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="3"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>Разработка</t>
+        </is>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="K4" s="64" t="inlineStr">
+      <c r="K6" s="31"/>
+      <c r="L6" s="32"/>
+    </row>
+    <row r="7" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>.</t>
         </is>
       </c>
-      <c r="L4" s="63" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="J7" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="31"/>
+      <c r="L7" s="32"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="B8" s="3"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="69" t="inlineStr">
-        <is>
-          <t>Дата:</t>
-        </is>
-      </c>
-      <c r="C5" s="61" t="inlineStr">
-        <is>
-          <t>13.10.2026</t>
-        </is>
-      </c>
-      <c r="D5" s="69" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="35" t="n"/>
-      <c r="G5" s="69" t="n"/>
-      <c r="H5" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J5" s="70" t="inlineStr">
-        <is>
-          <t>Положительно</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>Нет зависимости</t>
-        </is>
-      </c>
-      <c r="L5" s="70" t="inlineStr">
-        <is>
-          <t>Отрицательно</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="69" t="inlineStr">
-        <is>
-          <t>Этап (КТ)</t>
-        </is>
-      </c>
-      <c r="C6" s="61" t="inlineStr">
-        <is>
-          <t>Разработка</t>
-        </is>
-      </c>
-      <c r="D6" s="69" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="35" t="n"/>
-      <c r="G6" s="69" t="inlineStr">
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="K6" s="31" t="n"/>
-      <c r="L6" s="32" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="69" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="69" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="69" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="J7" s="71" t="inlineStr">
-        <is>
-          <t>Соотношение:</t>
-        </is>
-      </c>
-      <c r="K7" s="31" t="n"/>
-      <c r="L7" s="32" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="69" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="69" t="n"/>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="35" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="G8" s="69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="33" t="n">
+      <c r="J8" s="33">
         <v>9</v>
       </c>
-      <c r="K8" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="33" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="69" t="n"/>
-      <c r="C9" s="48" t="inlineStr">
-        <is>
-          <t>Направления улучшений (↑,0,↓)</t>
-        </is>
+      <c r="K8" s="33">
+        <v>3</v>
+      </c>
+      <c r="L8" s="33">
+        <v>1</v>
+      </c>
+      <c r="M8" s="33"/>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="B9" s="3"/>
+      <c r="C9" s="48" t="s">
+        <v>21</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -1278,133 +2067,94 @@
           <t>↑</t>
         </is>
       </c>
-      <c r="J9" s="34" t="inlineStr">
-        <is>
-          <t>Сильно</t>
-        </is>
-      </c>
-      <c r="K9" s="34" t="inlineStr">
-        <is>
-          <t>Средне</t>
-        </is>
-      </c>
-      <c r="L9" s="34" t="inlineStr">
-        <is>
-          <t>Слабо</t>
-        </is>
-      </c>
-      <c r="M9" s="34" t="inlineStr">
-        <is>
-          <t>Отсутствует</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="26" t="n"/>
-      <c r="B10" s="72" t="inlineStr">
-        <is>
-          <t>Мин.: 1,
-Макс.: 5</t>
-        </is>
-      </c>
-      <c r="C10" s="60" t="inlineStr">
-        <is>
-          <t>3. Функциональные требования
-→</t>
-        </is>
+      <c r="J9" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="24" ns2:dyDescent="0.2">
+      <c r="A10" s="26"/>
+      <c r="B10" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>22</v>
       </c>
       <c r="D10" s="76" t="inlineStr">
         <is>
-          <t>Себестоимость/цена, ₽
-(цел.: ≤650 / 799)</t>
+          <t>Себестоимость/цена, ₽</t>
         </is>
       </c>
       <c r="E10" s="76" t="inlineStr">
         <is>
-          <t>Время сохранения тепла, ч
-(цел.: ≥6)</t>
+          <t>Сохранение тепла, ч</t>
         </is>
       </c>
       <c r="F10" s="76" t="inlineStr">
         <is>
-          <t>Качество уплотнителя и
-эргономика крышки/ручки, балл
-(цел.: ≥4,5/5)</t>
+          <t>Герметичность/эргономика крышки, балл</t>
         </is>
       </c>
       <c r="G10" s="76" t="inlineStr">
         <is>
-          <t>Масса/объём/горловина
-(цел.: ≤320 г; 450 мл; ≥70 мм)</t>
+          <t>Масса, объём, удобство мойки</t>
         </is>
       </c>
       <c r="H10" s="76" t="inlineStr">
         <is>
-          <t>Материал корпуса и доля
-переработанных материалов, %
-(цел.: сталь 18/8; ≥35%)</t>
-        </is>
-      </c>
-      <c r="I10" s="26" t="n"/>
-      <c r="J10" s="78" t="inlineStr">
-        <is>
-          <t>Оценка: Слабо: 1, Сильно: 5</t>
-        </is>
-      </c>
-      <c r="K10" s="79" t="n"/>
-      <c r="L10" s="79" t="n"/>
-      <c r="M10" s="79" t="n"/>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="49" t="inlineStr">
-        <is>
-          <t>2. Важность для
-потребителя</t>
-        </is>
-      </c>
-      <c r="C11" s="59" t="inlineStr">
-        <is>
-          <t>1. Требования потребителя
-↓</t>
-        </is>
-      </c>
-      <c r="D11" s="80" t="n"/>
-      <c r="E11" s="80" t="n"/>
-      <c r="F11" s="80" t="n"/>
-      <c r="G11" s="80" t="n"/>
-      <c r="H11" s="80" t="n"/>
-      <c r="I11" s="73" t="inlineStr">
-        <is>
-          <t>Коеф конкурентоспособности ИО</t>
-        </is>
-      </c>
-      <c r="J11" s="50" t="inlineStr">
-        <is>
-          <t>Исслед. Обр</t>
-        </is>
-      </c>
-      <c r="K11" s="49" t="inlineStr">
-        <is>
-          <t>Конкурент 1</t>
-        </is>
-      </c>
-      <c r="L11" s="49" t="inlineStr">
-        <is>
-          <t>Конкурент 2</t>
-        </is>
-      </c>
-      <c r="M11" s="49" t="inlineStr">
-        <is>
-          <t>Конкурент 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="14" t="n">
+          <t>Материал и доля переработки, %</t>
+        </is>
+      </c>
+      <c r="I10" s="26"/>
+      <c r="J10" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="78"/>
+      <c r="L10" s="78"/>
+      <c r="M10" s="78"/>
+    </row>
+    <row r="11" spans="1:13" ht="36" ns2:dyDescent="0.2">
+      <c r="A11" s="35"/>
+      <c r="B11" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" s="49" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A12" s="68">
+        <v>1</v>
+      </c>
+      <c r="B12" s="14">
         <v>5</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1412,43 +2162,43 @@
           <t>Доступная цена для студента</t>
         </is>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D12" s="39">
         <v>9</v>
       </c>
-      <c r="E12" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="39" t="n">
+      <c r="E12" s="39">
+        <v>1</v>
+      </c>
+      <c r="F12" s="39">
+        <v>1</v>
+      </c>
+      <c r="G12" s="39">
+        <v>3</v>
+      </c>
+      <c r="H12" s="39">
         <v>1</v>
       </c>
       <c r="I12" s="51">
         <f>J12/MAX(K12:M12)</f>
-        <v/>
-      </c>
-      <c r="J12" s="36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J12" s="36">
         <v>4</v>
       </c>
-      <c r="K12" s="37" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="36" t="n">
+      <c r="K12" s="37">
+        <v>5</v>
+      </c>
+      <c r="L12" s="36">
+        <v>4</v>
+      </c>
+      <c r="M12" s="37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A13" s="68">
         <v>2</v>
       </c>
-      <c r="M12" s="37" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="14">
         <v>5</v>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1456,43 +2206,43 @@
           <t>Долго сохраняет температуру напитка</t>
         </is>
       </c>
-      <c r="D13" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="39" t="n">
+      <c r="D13" s="39">
+        <v>1</v>
+      </c>
+      <c r="E13" s="39">
         <v>9</v>
       </c>
-      <c r="F13" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="39" t="n">
+      <c r="F13" s="39">
+        <v>3</v>
+      </c>
+      <c r="G13" s="39">
+        <v>1</v>
+      </c>
+      <c r="H13" s="39">
         <v>1</v>
       </c>
       <c r="I13" s="51">
         <f>J13/MAX(K13:M13)</f>
-        <v/>
-      </c>
-      <c r="J13" s="38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J13" s="38">
         <v>4</v>
       </c>
-      <c r="K13" s="39" t="n">
+      <c r="K13" s="39">
         <v>5</v>
       </c>
-      <c r="L13" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" s="39" t="n">
+      <c r="L13" s="38">
+        <v>3</v>
+      </c>
+      <c r="M13" s="39">
         <v>4</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" s="14" t="n">
+    <row r="14" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A14" s="68">
+        <v>3</v>
+      </c>
+      <c r="B14" s="14">
         <v>5</v>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1500,87 +2250,87 @@
           <t>Герметичность (не протекает в рюкзаке)</t>
         </is>
       </c>
-      <c r="D14" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="39" t="n">
+      <c r="D14" s="39">
+        <v>1</v>
+      </c>
+      <c r="E14" s="39">
+        <v>3</v>
+      </c>
+      <c r="F14" s="39">
         <v>9</v>
       </c>
-      <c r="G14" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="39" t="n">
+      <c r="G14" s="39">
+        <v>1</v>
+      </c>
+      <c r="H14" s="39">
         <v>1</v>
       </c>
       <c r="I14" s="51">
         <f>J14/MAX(K14:M14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J14" s="38">
         <v>4</v>
       </c>
-      <c r="K14" s="39" t="n">
+      <c r="K14" s="39">
+        <v>5</v>
+      </c>
+      <c r="L14" s="38">
+        <v>3</v>
+      </c>
+      <c r="M14" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A15" s="68">
         <v>4</v>
       </c>
-      <c r="L14" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" s="39" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="68" t="n">
+      <c r="B15" s="14">
         <v>4</v>
       </c>
-      <c r="B15" s="14" t="n">
-        <v>4</v>
-      </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Небольшой вес</t>
         </is>
       </c>
-      <c r="D15" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="39" t="n">
+      <c r="D15" s="39">
+        <v>3</v>
+      </c>
+      <c r="E15" s="39">
+        <v>1</v>
+      </c>
+      <c r="F15" s="39">
+        <v>1</v>
+      </c>
+      <c r="G15" s="39">
         <v>9</v>
       </c>
-      <c r="H15" s="39" t="n">
+      <c r="H15" s="39">
         <v>3</v>
       </c>
       <c r="I15" s="51">
         <f>J15/MAX(K15:M15)</f>
-        <v/>
-      </c>
-      <c r="J15" s="38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J15" s="38">
         <v>5</v>
       </c>
-      <c r="K15" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="38" t="n">
+      <c r="K15" s="39">
+        <v>3</v>
+      </c>
+      <c r="L15" s="38">
         <v>4</v>
       </c>
-      <c r="M15" s="39" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="68" t="n">
+      <c r="M15" s="39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A16" s="68">
         <v>5</v>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="14">
         <v>4</v>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1588,43 +2338,43 @@
           <t>Достаточная вместимость</t>
         </is>
       </c>
-      <c r="D16" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="39" t="n">
+      <c r="D16" s="39">
+        <v>1</v>
+      </c>
+      <c r="E16" s="39">
+        <v>3</v>
+      </c>
+      <c r="F16" s="39">
+        <v>1</v>
+      </c>
+      <c r="G16" s="39">
         <v>9</v>
       </c>
-      <c r="H16" s="39" t="n">
+      <c r="H16" s="39">
         <v>1</v>
       </c>
       <c r="I16" s="51">
         <f>J16/MAX(K16:M16)</f>
-        <v/>
-      </c>
-      <c r="J16" s="38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J16" s="38">
         <v>4</v>
       </c>
-      <c r="K16" s="39" t="n">
+      <c r="K16" s="39">
         <v>5</v>
       </c>
-      <c r="L16" s="38" t="n">
+      <c r="L16" s="38">
         <v>4</v>
       </c>
-      <c r="M16" s="39" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="68" t="n">
+      <c r="M16" s="39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A17" s="68">
         <v>6</v>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="14">
         <v>3</v>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1632,43 +2382,43 @@
           <t>Удобство мытья</t>
         </is>
       </c>
-      <c r="D17" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" s="39" t="n">
+      <c r="D17" s="39">
+        <v>1</v>
+      </c>
+      <c r="E17" s="39">
+        <v>1</v>
+      </c>
+      <c r="F17" s="39">
+        <v>3</v>
+      </c>
+      <c r="G17" s="39">
         <v>9</v>
       </c>
-      <c r="H17" s="39" t="n">
+      <c r="H17" s="39">
         <v>3</v>
       </c>
       <c r="I17" s="51">
         <f>J17/MAX(K17:M17)</f>
-        <v/>
-      </c>
-      <c r="J17" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="38">
         <v>4</v>
       </c>
-      <c r="K17" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" s="38" t="n">
+      <c r="K17" s="39">
+        <v>3</v>
+      </c>
+      <c r="L17" s="38">
         <v>2</v>
       </c>
-      <c r="M17" s="39" t="n">
+      <c r="M17" s="39">
         <v>4</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="68" t="n">
+    <row r="18" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A18" s="68">
         <v>7</v>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="14">
         <v>4</v>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -1676,43 +2426,43 @@
           <t>Прочность при повседневном использовании</t>
         </is>
       </c>
-      <c r="D18" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" s="39" t="n">
+      <c r="D18" s="39">
+        <v>1</v>
+      </c>
+      <c r="E18" s="39">
+        <v>3</v>
+      </c>
+      <c r="F18" s="39">
+        <v>3</v>
+      </c>
+      <c r="G18" s="39">
+        <v>3</v>
+      </c>
+      <c r="H18" s="39">
         <v>9</v>
       </c>
       <c r="I18" s="51">
         <f>J18/MAX(K18:M18)</f>
-        <v/>
-      </c>
-      <c r="J18" s="38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J18" s="38">
         <v>4</v>
       </c>
-      <c r="K18" s="39" t="n">
+      <c r="K18" s="39">
         <v>5</v>
       </c>
-      <c r="L18" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" s="39" t="n">
+      <c r="L18" s="38">
+        <v>3</v>
+      </c>
+      <c r="M18" s="39">
         <v>4</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="68" t="n">
+    <row r="19" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A19" s="68">
         <v>8</v>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="14">
         <v>3</v>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -1720,43 +2470,43 @@
           <t>Экологичность материалов и упаковки</t>
         </is>
       </c>
-      <c r="D19" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="39" t="n">
+      <c r="D19" s="39">
+        <v>3</v>
+      </c>
+      <c r="E19" s="39">
+        <v>1</v>
+      </c>
+      <c r="F19" s="39">
+        <v>1</v>
+      </c>
+      <c r="G19" s="39">
+        <v>1</v>
+      </c>
+      <c r="H19" s="39">
         <v>9</v>
       </c>
       <c r="I19" s="51">
         <f>J19/MAX(K19:M19)</f>
-        <v/>
-      </c>
-      <c r="J19" s="38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J19" s="38">
+        <v>3</v>
+      </c>
+      <c r="K19" s="39">
         <v>5</v>
       </c>
-      <c r="K19" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="M19" s="39" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="68" t="n">
+      <c r="L19" s="38">
+        <v>4</v>
+      </c>
+      <c r="M19" s="39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A20" s="68">
         <v>9</v>
       </c>
-      <c r="B20" s="14" t="n">
+      <c r="B20" s="14">
         <v>4</v>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -1764,308 +2514,309 @@
           <t>Удобство переноски и питья на ходу</t>
         </is>
       </c>
-      <c r="D20" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="39" t="n">
+      <c r="D20" s="39">
+        <v>1</v>
+      </c>
+      <c r="E20" s="39">
+        <v>3</v>
+      </c>
+      <c r="F20" s="39">
         <v>9</v>
       </c>
-      <c r="G20" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="H20" s="39" t="n">
+      <c r="G20" s="39">
+        <v>3</v>
+      </c>
+      <c r="H20" s="39">
         <v>1</v>
       </c>
       <c r="I20" s="51">
         <f>J20/MAX(K20:M20)</f>
-        <v/>
-      </c>
-      <c r="J20" s="38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J20" s="38">
+        <v>4</v>
+      </c>
+      <c r="K20" s="39">
         <v>5</v>
       </c>
-      <c r="K20" s="39" t="n">
+      <c r="L20" s="38">
+        <v>3</v>
+      </c>
+      <c r="M20" s="39">
         <v>4</v>
       </c>
-      <c r="L20" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="M20" s="39" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="26" t="n"/>
-      <c r="B21" s="46" t="n"/>
-      <c r="C21" s="52" t="inlineStr">
-        <is>
-          <t>Техническая важность (расчет)</t>
-        </is>
+    </row>
+    <row r="21" spans="1:13" ht="12.75" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A21" s="26"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="52" t="s">
+        <v>24</v>
       </c>
       <c r="D21" s="56">
         <f>SUMPRODUCT($B$12:$B$20,D12:D20)</f>
-        <v/>
+        <v>91</v>
       </c>
       <c r="E21" s="56">
         <f>SUMPRODUCT($B$12:$B$20,E12:E20)</f>
-        <v/>
+        <v>111</v>
       </c>
       <c r="F21" s="56">
         <f>SUMPRODUCT($B$12:$B$20,F12:F20)</f>
-        <v/>
+        <v>133</v>
       </c>
       <c r="G21" s="56">
         <f>SUMPRODUCT($B$12:$B$20,G12:G20)</f>
-        <v/>
+        <v>151</v>
       </c>
       <c r="H21" s="56">
         <f>SUMPRODUCT($B$12:$B$20,H12:H20)</f>
-        <v/>
+        <v>107</v>
       </c>
       <c r="I21" s="5">
         <f>SUM(I12:I20)</f>
-        <v/>
-      </c>
-      <c r="J21" s="74" t="n"/>
-      <c r="K21" s="81" t="n"/>
-      <c r="L21" s="81" t="n"/>
-      <c r="M21" s="81" t="n"/>
-    </row>
-    <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="26" t="n"/>
-      <c r="B22" s="46" t="n"/>
-      <c r="C22" s="53" t="inlineStr">
-        <is>
-          <t>Важность, %</t>
-        </is>
+        <v>7.65</v>
+      </c>
+      <c r="J21" s="74"/>
+      <c r="K21" s="74"/>
+      <c r="L21" s="74"/>
+      <c r="M21" s="74"/>
+    </row>
+    <row r="22" spans="1:13" ht="12.75" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A22" s="26"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="53" t="s">
+        <v>25</v>
       </c>
       <c r="D22" s="57">
         <f>D21/$I$22</f>
-        <v/>
+        <v>0.153457</v>
       </c>
       <c r="E22" s="57">
         <f>E21/$I$22</f>
-        <v/>
+        <v>0.187184</v>
       </c>
       <c r="F22" s="57">
         <f>F21/$I$22</f>
-        <v/>
+        <v>0.224283</v>
       </c>
       <c r="G22" s="57">
         <f>G21/$I$22</f>
-        <v/>
+        <v>0.254637</v>
       </c>
       <c r="H22" s="57">
         <f>H21/$I$22</f>
-        <v/>
+        <v>0.180438</v>
       </c>
       <c r="I22" s="6">
         <f>SUM(D21:H21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="26" t="n"/>
-      <c r="B23" s="46" t="n"/>
-      <c r="C23" s="53" t="inlineStr">
-        <is>
-          <t>Приоритетность (топ n)</t>
-        </is>
+        <v>593</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="12.75" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A23" s="26"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="53" t="s">
+        <v>26</v>
       </c>
       <c r="D23" s="58">
         <f>RANK(D25,$D$25:$H$25,0)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="E23" s="58">
         <f>RANK(E25,$D$25:$H$25,0)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F23" s="58">
         <f>RANK(F25,$D$25:$H$25,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="G23" s="58">
         <f>RANK(G25,$D$25:$H$25,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H23" s="58">
         <f>RANK(H25,$D$25:$H$25,0)</f>
-        <v/>
-      </c>
-      <c r="I23" s="7" t="n"/>
-    </row>
-    <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="26" t="n"/>
-      <c r="B24" s="41" t="n"/>
-      <c r="C24" s="54" t="inlineStr">
-        <is>
-          <t>Сумма соотношений при Ki&lt;0,7</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="1:13" ht="12.75" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A24" s="26"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="54" t="s">
+        <v>33</v>
       </c>
       <c r="D24" s="42">
         <f>SUMPRODUCT((($I$12:$I$20&lt;0.7)+0),D12:D20)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E24" s="42">
         <f>SUMPRODUCT((($I$12:$I$20&lt;0.7)+0),E12:E20)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F24" s="42">
         <f>SUMPRODUCT((($I$12:$I$20&lt;0.7)+0),F12:F20)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G24" s="42">
         <f>SUMPRODUCT((($I$12:$I$20&lt;0.7)+0),G12:G20)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H24" s="42">
         <f>SUMPRODUCT((($I$12:$I$20&lt;0.7)+0),H12:H20)</f>
-        <v/>
-      </c>
-      <c r="I24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="12.75" customHeight="1">
-      <c r="A25" s="26" t="n"/>
-      <c r="B25" s="41" t="n"/>
-      <c r="C25" s="55" t="inlineStr">
-        <is>
-          <t>Приоритет для улучшения</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" spans="1:13" ht="12.75" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A25" s="26"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="55" t="s">
+        <v>27</v>
       </c>
       <c r="D25" s="11">
         <f>D21*(1+IF(MAX($D$24:$H$24)=0,0,D24/MAX($D$24:$H$24)))</f>
-        <v/>
+        <v>121.333333</v>
       </c>
       <c r="E25" s="11">
         <f>E21*(1+IF(MAX($D$24:$H$24)=0,0,E24/MAX($D$24:$H$24)))</f>
-        <v/>
+        <v>123.333333</v>
       </c>
       <c r="F25" s="11">
         <f>F21*(1+IF(MAX($D$24:$H$24)=0,0,F24/MAX($D$24:$H$24)))</f>
-        <v/>
+        <v>147.777778</v>
       </c>
       <c r="G25" s="11">
         <f>G21*(1+IF(MAX($D$24:$H$24)=0,0,G24/MAX($D$24:$H$24)))</f>
-        <v/>
+        <v>167.777778</v>
       </c>
       <c r="H25" s="11">
         <f>H21*(1+IF(MAX($D$24:$H$24)=0,0,H24/MAX($D$24:$H$24)))</f>
-        <v/>
-      </c>
-      <c r="I25" s="43" t="n"/>
-    </row>
-    <row r="26" ht="12.75" customHeight="1">
-      <c r="A26" s="26" t="n"/>
-      <c r="C26" s="44" t="n"/>
-      <c r="D26" s="45" t="n"/>
-      <c r="E26" s="45" t="n"/>
-      <c r="F26" s="45" t="n"/>
-      <c r="G26" s="45" t="n"/>
-      <c r="H26" s="45" t="n"/>
-      <c r="I26" s="26" t="n"/>
-    </row>
-    <row r="27" ht="12.75" customHeight="1">
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Comments/Conclusion:</t>
-        </is>
+        <v>214</v>
+      </c>
+      <c r="I25" s="43"/>
+    </row>
+    <row r="26" spans="1:13" ht="12.75" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A26" s="26"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="26"/>
+    </row>
+    <row r="27" spans="1:13" ht="12.75" ns2:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Приоритеты улучшения: максимизировать сохранение тепла и надежность герметичной крышки, затем снижать цену без потери прочности и экологичности материалов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="17" t="n"/>
-      <c r="H28" s="17" t="n"/>
-      <c r="I28" s="17" t="n"/>
-      <c r="J28" s="17" t="n"/>
-      <c r="K28" s="17" t="n"/>
-      <c r="L28" s="17" t="n"/>
-      <c r="M28" s="18" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="22" t="n"/>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="24" t="n"/>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="24" t="n"/>
-      <c r="G29" s="24" t="n"/>
-      <c r="H29" s="24" t="n"/>
-      <c r="I29" s="24" t="n"/>
-      <c r="J29" s="24" t="n"/>
-      <c r="K29" s="24" t="n"/>
-      <c r="L29" s="24" t="n"/>
-      <c r="M29" s="25" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="20" t="n"/>
-      <c r="G30" s="20" t="n"/>
-      <c r="H30" s="20" t="n"/>
-      <c r="I30" s="20" t="n"/>
-      <c r="J30" s="20" t="n"/>
-      <c r="K30" s="20" t="n"/>
-      <c r="L30" s="20" t="n"/>
-      <c r="M30" s="21" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="46" t="n"/>
-      <c r="C31" s="46" t="n"/>
-      <c r="D31" s="46" t="n"/>
-      <c r="E31" s="46" t="n"/>
-      <c r="F31" s="46" t="n"/>
-      <c r="G31" s="46" t="n"/>
-      <c r="H31" s="46" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="75" t="n"/>
-    </row>
-    <row r="34" ht="12.75" customHeight="1">
-      <c r="B34" s="65" t="n"/>
-    </row>
-    <row r="35" ht="12.75" customHeight="1">
-      <c r="B35" s="66" t="n"/>
-    </row>
-    <row r="36" ht="12.75" customHeight="1">
-      <c r="B36" s="66" t="n"/>
-    </row>
-    <row r="37" ht="12.75" customHeight="1">
-      <c r="B37" s="66" t="n"/>
-    </row>
-    <row r="38" ht="12.75" customHeight="1">
-      <c r="B38" s="66" t="n"/>
-    </row>
-    <row r="39" ht="12.75" customHeight="1">
-      <c r="B39" s="65" t="n"/>
-    </row>
-    <row r="40" ht="12.75" customHeight="1">
-      <c r="B40" s="67" t="n"/>
+          <t>Приоритеты улучшения: удержание тепла и герметичность крышки при сохранении доступной цены, прочности и экологичности.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ns2:dyDescent="0.2">
+      <c r="B28" s="15"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="18"/>
+    </row>
+    <row r="29" spans="1:13" ns2:dyDescent="0.2">
+      <c r="B29" s="22"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="25"/>
+    </row>
+    <row r="30" spans="1:13" ns2:dyDescent="0.2">
+      <c r="B30" s="19"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="21"/>
+    </row>
+    <row r="31" spans="1:13" ns2:dyDescent="0.2">
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+    </row>
+    <row r="32" spans="1:13" ht="15" ns2:dyDescent="0.2">
+      <c r="B32" s="75"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+      <c r="I32" s="75"/>
+      <c r="J32" s="75"/>
+      <c r="K32" s="75"/>
+      <c r="L32" s="75"/>
+      <c r="M32" s="75"/>
+    </row>
+    <row r="34" spans="2:2" ht="12.75" ns2:dyDescent="0.2">
+      <c r="B34" s="65"/>
+    </row>
+    <row r="35" spans="2:2" ht="12.75" ns2:dyDescent="0.2">
+      <c r="B35" s="66"/>
+    </row>
+    <row r="36" spans="2:2" ht="12.75" ns2:dyDescent="0.2">
+      <c r="B36" s="66"/>
+    </row>
+    <row r="37" spans="2:2" ht="12.75" ns2:dyDescent="0.2">
+      <c r="B37" s="66"/>
+    </row>
+    <row r="38" spans="2:2" ht="12.75" ns2:dyDescent="0.2">
+      <c r="B38" s="66"/>
+    </row>
+    <row r="39" spans="2:2" ht="12.75" ns2:dyDescent="0.2">
+      <c r="B39" s="65"/>
+    </row>
+    <row r="40" spans="2:2" ht="12.75" ns2:dyDescent="0.2">
+      <c r="B40" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="B32:M32"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
     <mergeCell ref="J10:M10"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B32:M32"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="G10:G11"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" scale="95"/>
+  <pageSetup scale="95" orientation="landscape" ns3:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing ns3:id="rId2"/>
 </worksheet>
 </file>
--- a/дом качества — экономичная термокружка для студентов.xlsx
+++ b/дом качества — экономичная термокружка для студентов.xlsx
@@ -996,7 +996,7 @@
                 <a:latin typeface="+mn-lt"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>.</a:t>
+              <a:t>+</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
@@ -1049,7 +1049,7 @@
                 <a:latin typeface="+mn-lt"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>.</a:t>
+              <a:t>-</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
@@ -1102,7 +1102,7 @@
                 <a:latin typeface="+mn-lt"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>.</a:t>
+              <a:t>+</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
@@ -1155,7 +1155,7 @@
                 <a:latin typeface="+mn-lt"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>.</a:t>
+              <a:t>-</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
@@ -1208,7 +1208,7 @@
                 <a:latin typeface="+mn-lt"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>.</a:t>
+              <a:t>+</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
@@ -1261,7 +1261,7 @@
                 <a:latin typeface="+mn-lt"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>.</a:t>
+              <a:t>-</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
@@ -1314,7 +1314,7 @@
                 <a:latin typeface="+mn-lt"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>.</a:t>
+              <a:t>+</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
@@ -1367,7 +1367,7 @@
                 <a:latin typeface="+mn-lt"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>.</a:t>
+              <a:t>-</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
@@ -1420,7 +1420,7 @@
                 <a:latin typeface="+mn-lt"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>.</a:t>
+              <a:t>+</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
@@ -1473,7 +1473,7 @@
                 <a:latin typeface="+mn-lt"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>.</a:t>
+              <a:t>-</a:t>
             </a:r>
           </a:p>
         </xdr:txBody>
